--- a/Datos_Pagos.xlsx
+++ b/Datos_Pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Grupo_Pioneros\4-Programas_Python\Consulta_Nube2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26291C0E-D4F7-4449-BEC6-E17DB044FEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700F2FB-C7CC-4BF7-BACB-FC08B4596A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{27EA49FF-17D2-46CF-85DB-C764D3284ABD}"/>
   </bookViews>
@@ -1712,14 +1712,14 @@
         <v>37</v>
       </c>
       <c r="Y4" s="9">
+        <v>11980</v>
+      </c>
+      <c r="Z4" s="9">
         <v>13500</v>
-      </c>
-      <c r="Z4" s="9">
-        <v>11980</v>
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB4" s="10">
         <v>46022</v>
@@ -1767,14 +1767,14 @@
         <v>40</v>
       </c>
       <c r="Y5" s="9">
+        <v>8050</v>
+      </c>
+      <c r="Z5" s="9">
         <v>8500</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>8050</v>
       </c>
       <c r="AA5" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB5" s="10">
         <v>46022</v>
@@ -1846,14 +1846,14 @@
         <v>37</v>
       </c>
       <c r="Y6" s="9">
+        <v>12750</v>
+      </c>
+      <c r="Z6" s="9">
         <v>13500</v>
-      </c>
-      <c r="Z6" s="9">
-        <v>12750</v>
       </c>
       <c r="AA6" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>-750</v>
       </c>
       <c r="AB6" s="10">
         <v>46022</v>
@@ -1986,14 +1986,14 @@
         <v>37</v>
       </c>
       <c r="Y8" s="9">
+        <v>10018.834999999999</v>
+      </c>
+      <c r="Z8" s="9">
         <v>11538.834999999999</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>10018.834999999999</v>
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB8" s="10">
         <v>46022</v>
@@ -2071,14 +2071,14 @@
         <v>25</v>
       </c>
       <c r="Y9" s="9">
+        <v>3050</v>
+      </c>
+      <c r="Z9" s="9">
         <v>3500</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>3050</v>
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB9" s="10">
         <v>46022</v>
@@ -2153,14 +2153,14 @@
         <v>25</v>
       </c>
       <c r="Y10" s="9">
+        <v>17250</v>
+      </c>
+      <c r="Z10" s="9">
         <v>18000</v>
-      </c>
-      <c r="Z10" s="9">
-        <v>17250</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>-750</v>
       </c>
       <c r="AB10" s="10">
         <v>46022</v>
@@ -2854,14 +2854,14 @@
         <v>25</v>
       </c>
       <c r="Y21" s="9">
+        <v>11430</v>
+      </c>
+      <c r="Z21" s="9">
         <v>12950</v>
-      </c>
-      <c r="Z21" s="9">
-        <v>11430</v>
       </c>
       <c r="AA21" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB21" s="10">
         <v>46022</v>
@@ -2936,14 +2936,14 @@
         <v>25</v>
       </c>
       <c r="Y22" s="9">
+        <v>12870</v>
+      </c>
+      <c r="Z22" s="9">
         <v>13320</v>
-      </c>
-      <c r="Z22" s="9">
-        <v>12870</v>
       </c>
       <c r="AA22" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB22" s="10">
         <v>46022</v>
@@ -3018,14 +3018,14 @@
         <v>25</v>
       </c>
       <c r="Y23" s="9">
+        <v>12740</v>
+      </c>
+      <c r="Z23" s="9">
         <v>13490</v>
-      </c>
-      <c r="Z23" s="9">
-        <v>12740</v>
       </c>
       <c r="AA23" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>-750</v>
       </c>
       <c r="AB23" s="10">
         <v>46022</v>
@@ -3393,14 +3393,14 @@
         <v>25</v>
       </c>
       <c r="Y29" s="9">
+        <v>9473.8070000000007</v>
+      </c>
+      <c r="Z29" s="9">
         <v>10993.807000000001</v>
-      </c>
-      <c r="Z29" s="9">
-        <v>9473.8070000000007</v>
       </c>
       <c r="AA29" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB29" s="10">
         <v>46022</v>
@@ -3475,14 +3475,14 @@
         <v>25</v>
       </c>
       <c r="Y30" s="9">
+        <v>18050</v>
+      </c>
+      <c r="Z30" s="9">
         <v>18500</v>
-      </c>
-      <c r="Z30" s="9">
-        <v>18050</v>
       </c>
       <c r="AA30" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB30" s="10">
         <v>46022</v>
@@ -3621,14 +3621,14 @@
         <v>25</v>
       </c>
       <c r="Y32" s="9">
+        <v>9210</v>
+      </c>
+      <c r="Z32" s="9">
         <v>10730</v>
-      </c>
-      <c r="Z32" s="9">
-        <v>9210</v>
       </c>
       <c r="AA32" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB32" s="10">
         <v>46022</v>
@@ -3664,14 +3664,14 @@
         <v>24000</v>
       </c>
       <c r="Y33" s="9">
+        <v>551</v>
+      </c>
+      <c r="Z33" s="9">
         <v>1001</v>
-      </c>
-      <c r="Z33" s="9">
-        <v>551</v>
       </c>
       <c r="AA33" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB33" s="10">
         <v>46022</v>
@@ -3807,14 +3807,14 @@
         <v>25</v>
       </c>
       <c r="Y35" s="9">
+        <v>12980</v>
+      </c>
+      <c r="Z35" s="9">
         <v>14500</v>
-      </c>
-      <c r="Z35" s="9">
-        <v>12980</v>
       </c>
       <c r="AA35" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB35" s="10">
         <v>46022</v>
@@ -3877,14 +3877,14 @@
         <v>25</v>
       </c>
       <c r="Y36" s="9">
+        <v>14050</v>
+      </c>
+      <c r="Z36" s="9">
         <v>14500</v>
-      </c>
-      <c r="Z36" s="9">
-        <v>14050</v>
       </c>
       <c r="AA36" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB36" s="10">
         <v>46022</v>
@@ -3956,14 +3956,14 @@
         <v>251</v>
       </c>
       <c r="Y37" s="9">
+        <v>22650</v>
+      </c>
+      <c r="Z37" s="9">
         <v>23400</v>
-      </c>
-      <c r="Z37" s="9">
-        <v>22650</v>
       </c>
       <c r="AA37" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>-750</v>
       </c>
       <c r="AB37" s="10">
         <v>46022</v>
@@ -4117,14 +4117,14 @@
         <v>291</v>
       </c>
       <c r="Y39" s="9">
+        <v>16480</v>
+      </c>
+      <c r="Z39" s="9">
         <v>18000</v>
-      </c>
-      <c r="Z39" s="9">
-        <v>16480</v>
       </c>
       <c r="AA39" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB39" s="10">
         <v>46022</v>
@@ -4199,14 +4199,14 @@
         <v>291</v>
       </c>
       <c r="Y40" s="9">
+        <v>17550</v>
+      </c>
+      <c r="Z40" s="9">
         <v>18000</v>
-      </c>
-      <c r="Z40" s="9">
-        <v>17550</v>
       </c>
       <c r="AA40" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB40" s="10">
         <v>46022</v>
@@ -4284,14 +4284,14 @@
         <v>25</v>
       </c>
       <c r="Y41" s="9">
+        <v>16480</v>
+      </c>
+      <c r="Z41" s="9">
         <v>18000</v>
-      </c>
-      <c r="Z41" s="9">
-        <v>16480</v>
       </c>
       <c r="AA41" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB41" s="10">
         <v>46022</v>
@@ -4366,14 +4366,14 @@
         <v>291</v>
       </c>
       <c r="Y42" s="9">
+        <v>63000</v>
+      </c>
+      <c r="Z42" s="9">
         <v>63450</v>
-      </c>
-      <c r="Z42" s="9">
-        <v>63000</v>
       </c>
       <c r="AA42" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB42" s="10">
         <v>46022</v>
@@ -4448,14 +4448,14 @@
         <v>25</v>
       </c>
       <c r="Y43" s="9">
+        <v>61930</v>
+      </c>
+      <c r="Z43" s="9">
         <v>63450</v>
-      </c>
-      <c r="Z43" s="9">
-        <v>61930</v>
       </c>
       <c r="AA43" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB43" s="10">
         <v>46022</v>
@@ -4530,14 +4530,14 @@
         <v>25</v>
       </c>
       <c r="Y44" s="9">
+        <v>16480</v>
+      </c>
+      <c r="Z44" s="9">
         <v>18000</v>
-      </c>
-      <c r="Z44" s="9">
-        <v>16480</v>
       </c>
       <c r="AA44" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>-1520</v>
       </c>
       <c r="AB44" s="10">
         <v>46022</v>
@@ -4606,14 +4606,14 @@
         <v>37</v>
       </c>
       <c r="Y45" s="9">
+        <v>73470</v>
+      </c>
+      <c r="Z45" s="9">
         <v>73920</v>
-      </c>
-      <c r="Z45" s="9">
-        <v>73470</v>
       </c>
       <c r="AA45" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>-450</v>
       </c>
       <c r="AB45" s="10">
         <v>46022</v>
@@ -4682,14 +4682,14 @@
         <v>256</v>
       </c>
       <c r="Y46" s="9">
+        <v>47250</v>
+      </c>
+      <c r="Z46" s="9">
         <v>48000</v>
-      </c>
-      <c r="Z46" s="9">
-        <v>47250</v>
       </c>
       <c r="AA46" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>-750</v>
       </c>
       <c r="AB46" s="10">
         <v>46022</v>

--- a/Datos_Pagos.xlsx
+++ b/Datos_Pagos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\consulta-pago-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70487CC-88F9-437C-B8E4-7CABBDC8A440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07B5699-AB49-4286-9F52-7F8AA1E274CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" xr2:uid="{27EA49FF-17D2-46CF-85DB-C764D3284ABD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{27EA49FF-17D2-46CF-85DB-C764D3284ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="Pagos" sheetId="2" r:id="rId1"/>
@@ -9388,13 +9388,13 @@
     <t>+569 78361588</t>
   </si>
   <si>
-    <t>pagos-real</t>
-  </si>
-  <si>
-    <t>cobros-plan</t>
-  </si>
-  <si>
     <t>Carlos Manuel Avila Jara (Catalina  Aguirre Rojas)</t>
+  </si>
+  <si>
+    <t>pagos</t>
+  </si>
+  <si>
+    <t>cobros</t>
   </si>
 </sst>
 </file>
@@ -9450,7 +9450,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9478,6 +9478,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares [0] 2" xfId="2" xr:uid="{D1358CCE-C6F2-47A9-8955-5F2313C0DFD7}"/>
@@ -9905,11 +9909,11 @@
       <c r="X1" t="s">
         <v>11</v>
       </c>
-      <c r="Y1" s="7" t="s">
-        <v>3113</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="Y1" s="11" t="s">
         <v>3114</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>3115</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>150</v>
@@ -40401,7 +40405,7 @@
         <v>45054</v>
       </c>
       <c r="P358" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="Q358" t="s">
         <v>2220</v>

--- a/Datos_Pagos.xlsx
+++ b/Datos_Pagos.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johny\Desktop\Grupo_Pioneros\4-Programas_Python\Consulta_Nube_NP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEE81AF-F843-4627-822A-2ED08DE985B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8074CA41-BA70-4FB2-951E-F013D7D76333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E2C6E29-C685-4D5B-B1ED-04E51F01A92E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Nube" sheetId="1" r:id="rId1"/>
+    <sheet name="Pagos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -9208,7 +9208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9224,6 +9224,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -9252,7 +9260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9273,6 +9281,7 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10099,7 +10108,7 @@
       <c r="X6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="10">
         <v>17400</v>
       </c>
       <c r="Z6" s="6">
